--- a/data/trans_camb/IP1010-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Edad-trans_camb.xlsx
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,83</t>
+          <t>-0,67; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,0</t>
+          <t>-2,22; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; -0,24</t>
+          <t>-2,09; -0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,49</t>
+          <t>-0,94; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; -0,25</t>
+          <t>-1,61; -0,24</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 266,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-2,97; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,22</t>
+          <t>-0,53; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,04</t>
+          <t>-0,34; 2,06</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,73; —</t>
+          <t>-60,86; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,78; —</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,05</t>
+          <t>-0,6; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,22; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>-0,29; 1,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,15</t>
+          <t>-0,95; 0,15</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,62</t>
+          <t>-0,27; 0,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,11</t>
+          <t>-0,48; 0,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,25</t>
+          <t>-0,93; 0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,71</t>
+          <t>-0,69; 0,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,24</t>
+          <t>-0,41; 0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,32</t>
+          <t>-0,45; 0,35</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,99; 102,59</t>
+          <t>-89,54; 118,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,72; 261,99</t>
+          <t>-71,73; 224,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 111,48</t>
+          <t>-72,93; 118,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 167,94</t>
+          <t>-72,31; 149,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Edad-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,82</t>
+          <t>-0,6; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,0</t>
+          <t>-1,73; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,24</t>
+          <t>-2,07; -0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,24</t>
+          <t>-1,96; -0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,6</t>
+          <t>-0,96; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,24</t>
+          <t>-1,31; -0,25</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,0</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,14</t>
+          <t>-0,39; 4,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,06</t>
+          <t>-0,25; 2,13</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,86; —</t>
+          <t>-68,7; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,78; —</t>
+          <t>-64,91; —</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,66</t>
+          <t>-0,6; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,49</t>
+          <t>-0,27; 1,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-0,84; 0,29</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,62</t>
+          <t>-0,28; 0,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,13</t>
+          <t>-0,5; 0,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,26</t>
+          <t>-0,92; 0,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,71</t>
+          <t>-0,62; 0,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,26</t>
+          <t>-0,5; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,35</t>
+          <t>-0,41; 0,32</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 118,28</t>
+          <t>-88,19; 88,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,73; 224,48</t>
+          <t>-71,0; 220,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 118,73</t>
+          <t>-79,6; 123,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,31; 149,18</t>
+          <t>-68,63; 145,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,1</t>
+          <t>-2,13; -0,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,11; -0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,24</t>
+          <t>-0,71; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; -0,24</t>
+          <t>-1,49; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,57</t>
+          <t>-0,89; 0,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,25</t>
+          <t>-1,39; -0,25</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>81,39%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 266,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,45; 4,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-1,71; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,13</t>
+          <t>-0,41; 2,04</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>176,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-53,73; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,7; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,91; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,5; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,52</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,29</t>
+          <t>-0,84; 0,15</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>134,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>134,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,61</t>
+          <t>-0,93; 0,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,12</t>
+          <t>-0,64; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,17</t>
+          <t>-0,26; 0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,72</t>
+          <t>-0,46; 0,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,25</t>
+          <t>-0,52; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-45,06%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>61,82%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-59,38%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-45,06%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,99; 102,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,72; 261,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 88,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,0; 220,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 123,77</t>
+          <t>-78,87; 111,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 145,27</t>
+          <t>-69,87; 167,94</t>
         </is>
       </c>
     </row>
